--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487067_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487067_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9291</v>
+        <v>12.4437</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1467</v>
+        <v>7.4471</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7825</v>
+        <v>4.9966</v>
       </c>
       <c r="G2" t="n">
         <v>7.4201</v>
@@ -610,13 +610,13 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4957</v>
+        <v>0.0188</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3391</v>
+        <v>-1.0387</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8434</v>
+        <v>1.0575</v>
       </c>
       <c r="V2" t="n">
         <v>5.1977</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4572</v>
+        <v>4.6248</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5043</v>
+        <v>-0.6045</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9616</v>
+        <v>5.2292</v>
       </c>
       <c r="G3" t="n">
         <v>3.9872</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.074</v>
+        <v>0.0935</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5816</v>
+        <v>-0.6818</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.7753</v>
       </c>
       <c r="V3" t="n">
         <v>-0.614</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0547</v>
+        <v>2.3353</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7127</v>
+        <v>-1.5125</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7675</v>
+        <v>3.8478</v>
       </c>
       <c r="G4" t="n">
         <v>3.5294</v>
@@ -766,13 +766,13 @@
         <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3312</v>
+        <v>-0.0506</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3087</v>
+        <v>-1.1084</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9776</v>
+        <v>1.0579</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1435</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7581</v>
+        <v>1.5375</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.1974</v>
+        <v>-2.8207</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9555</v>
+        <v>4.3582</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6597</v>
+        <v>4.1729</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1385</v>
+        <v>2.7241</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5212</v>
+        <v>1.4488</v>
       </c>
       <c r="J5" t="n">
-        <v>0.524</v>
+        <v>2.0226</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.29</v>
+        <v>0.6881</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.3345</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1357</v>
+        <v>2.1502</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4285</v>
+        <v>2.036</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2928</v>
+        <v>0.1142</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.386</v>
+        <v>-5.7902</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-7.7203</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6968</v>
+        <v>0.1272</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1507</v>
+        <v>-0.7224</v>
       </c>
       <c r="U5" t="n">
-        <v>2.8475</v>
+        <v>0.8497</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.2123</v>
+        <v>3.0277</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.6406</v>
+        <v>3.5994</v>
       </c>
       <c r="X5" t="n">
         <v>-0.5717</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6039</v>
+        <v>0.4405</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6205</v>
+        <v>-3.4978</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2244</v>
+        <v>3.9383</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1729</v>
+        <v>1.6597</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7241</v>
+        <v>1.1385</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4488</v>
+        <v>0.5212</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0226</v>
+        <v>0.524</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6881</v>
+        <v>-0.29</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3345</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>2.1502</v>
+        <v>1.1357</v>
       </c>
       <c r="N6" t="n">
-        <v>2.036</v>
+        <v>1.4285</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1142</v>
+        <v>-0.2928</v>
       </c>
       <c r="P6" t="n">
-        <v>-5.7902</v>
+        <v>-0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7.7203</v>
+        <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1937</v>
+        <v>1.3791</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5221</v>
+        <v>-0.4511</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7158</v>
+        <v>1.8302</v>
       </c>
       <c r="V6" t="n">
-        <v>3.0277</v>
+        <v>-2.2123</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5994</v>
+        <v>-1.6406</v>
       </c>
       <c r="X6" t="n">
         <v>-0.5717</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4193</v>
+        <v>-0.7534</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1857</v>
+        <v>-1.3859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7664</v>
+        <v>0.6325</v>
       </c>
       <c r="G7" t="n">
         <v>0.4233</v>
@@ -1000,13 +1000,13 @@
         <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5784</v>
+        <v>0.2442</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0172</v>
+        <v>-0.2174</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5955</v>
+        <v>0.4617</v>
       </c>
       <c r="V7" t="n">
         <v>-1.228</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1353</v>
+        <v>-1.5418</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.1964</v>
+        <v>-0.843</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0611</v>
+        <v>-0.6988</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1208</v>
+        <v>-0.4398</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4871</v>
+        <v>-0.207</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3663</v>
+        <v>-0.2328</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.1288</v>
+        <v>-0.6269</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.5669</v>
+        <v>-0.6676</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5619</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>1.008</v>
+        <v>0.1871</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0798</v>
+        <v>0.4606</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9282</v>
+        <v>-0.2735</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1231</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1785</v>
+        <v>-0.2601</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0556</v>
+        <v>-0.2161</v>
       </c>
       <c r="U8" t="n">
-        <v>1.123</v>
+        <v>-0.044</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8759</v>
+        <v>-1.8838</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0433</v>
+        <v>-5.5969</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8326</v>
+        <v>3.7131</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4398</v>
+        <v>-2.1208</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.207</v>
+        <v>-2.4871</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2328</v>
+        <v>0.3663</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6269</v>
+        <v>-3.1288</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6676</v>
+        <v>-2.5669</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>-0.5619</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1871</v>
+        <v>1.008</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4606</v>
+        <v>0.0798</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2735</v>
+        <v>0.9282</v>
       </c>
       <c r="P9" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q9" t="n">
+        <v>-2.1231</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.9301</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.345</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.5942</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.4164</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.1778</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1.228</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0177</v>
+        <v>-3.7969</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4578</v>
+        <v>-1.3233</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5598</v>
+        <v>-2.4736</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2804</v>
+        <v>0.3735</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6809</v>
+        <v>-0.649</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4006</v>
+        <v>1.0225</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3871</v>
+        <v>0.2931</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3871</v>
+        <v>-0.3416</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.6348</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1067</v>
+        <v>0.0804</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2939</v>
+        <v>-0.3073</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4006</v>
+        <v>0.3877</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1203</v>
+        <v>-0.1005</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0873</v>
+        <v>-0.6514</v>
       </c>
       <c r="U10" t="n">
-        <v>0.033</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0856</v>
+        <v>-3.6839</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0856</v>
+        <v>-3.6839</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3382</v>
+        <v>-4.0573</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6237</v>
+        <v>-2.6581</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7145</v>
+        <v>-1.3992</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3735</v>
+        <v>-1.2804</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.649</v>
+        <v>-1.6809</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0225</v>
+        <v>0.4006</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2931</v>
+        <v>-1.3871</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3416</v>
+        <v>-1.3871</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6348</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0804</v>
+        <v>0.1067</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3073</v>
+        <v>-0.2939</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3877</v>
+        <v>0.4006</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.386</v>
+        <v>-0.772</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.965</v>
+        <v>-1.158</v>
       </c>
       <c r="R11" t="n">
-        <v>0.579</v>
+        <v>0.386</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6418</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9518</v>
+        <v>-0.113</v>
       </c>
       <c r="U11" t="n">
-        <v>0.31</v>
+        <v>0.1937</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.6839</v>
+        <v>-2.0856</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.6839</v>
+        <v>-2.0856</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3712</v>
+        <v>-4.703</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.5479</v>
+        <v>-6.1474</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1767</v>
+        <v>1.4444</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5098</v>
@@ -1390,13 +1390,13 @@
         <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7733</v>
+        <v>-0.1051</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7442</v>
+        <v>-0.3437</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0291</v>
+        <v>0.2386</v>
       </c>
       <c r="V12" t="n">
         <v>1.228</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6454</v>
+        <v>4.645600000000003</v>
       </c>
       <c r="E13" t="n">
         <v>-18.943</v>
       </c>
       <c r="F13" t="n">
-        <v>23.5888</v>
+        <v>23.5885</v>
       </c>
       <c r="G13" t="n">
         <v>14.2153</v>
@@ -1453,7 +1453,7 @@
         <v>11.4855</v>
       </c>
       <c r="N13" t="n">
-        <v>7.608699999999999</v>
+        <v>7.608700000000001</v>
       </c>
       <c r="O13" t="n">
         <v>3.8769</v>
@@ -1468,13 +1468,13 @@
         <v>15.4406</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8575</v>
+        <v>1.8572</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.8889</v>
+        <v>-5.889</v>
       </c>
       <c r="U13" t="n">
-        <v>7.7465</v>
+        <v>7.746499999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.741899999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1791</v>
+        <v>5.8408</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6484</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5307</v>
+        <v>5.0923</v>
       </c>
       <c r="G14" t="n">
         <v>1.8558</v>
@@ -1546,13 +1546,13 @@
         <v>4.0532</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7396</v>
+        <v>-0.078</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0575</v>
+        <v>-0.9574</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3179</v>
+        <v>0.8794</v>
       </c>
       <c r="V14" t="n">
         <v>2.9049</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8988</v>
+        <v>4.0149</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.749</v>
+        <v>-0.2483</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6478</v>
+        <v>4.2632</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3796</v>
@@ -1624,13 +1624,13 @@
         <v>4.2462</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9221</v>
+        <v>-0.8061</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.9036</v>
+        <v>-1.4029</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0185</v>
+        <v>0.5968</v>
       </c>
       <c r="V15" t="n">
         <v>1.1474</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9326</v>
+        <v>1.457</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.2114</v>
+        <v>-4.3116</v>
       </c>
       <c r="F16" t="n">
-        <v>6.144</v>
+        <v>5.7686</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2571</v>
@@ -1702,13 +1702,13 @@
         <v>3.8602</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5248</v>
+        <v>0.0492</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8196</v>
+        <v>-0.9197</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3444</v>
+        <v>0.969</v>
       </c>
       <c r="V16" t="n">
         <v>0.7348</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6902</v>
+        <v>0.5768</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3909</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2993</v>
+        <v>0.4864</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0726</v>
@@ -1780,13 +1780,13 @@
         <v>0.193</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5698</v>
+        <v>0.4564</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3702</v>
+        <v>0.0697</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1996</v>
+        <v>0.3867</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3671</v>
+        <v>-0.4158</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5494</v>
+        <v>-5.5921</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1823</v>
+        <v>5.1763</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2898</v>
+        <v>-0.3165</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1563</v>
+        <v>0.3539</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1335</v>
+        <v>-0.6705</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.004</v>
+        <v>0.1833</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3364</v>
+        <v>0.0205</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6676</v>
+        <v>0.1628</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7141999999999999</v>
+        <v>-0.4998</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1801</v>
+        <v>0.3335</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5341</v>
+        <v>-0.8333</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.579</v>
+        <v>-0.965</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>-4.8252</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>3.8602</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5017</v>
+        <v>-0.6097</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1917</v>
+        <v>-1.236</v>
       </c>
       <c r="U18" t="n">
-        <v>0.31</v>
+        <v>0.6263</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4755</v>
       </c>
       <c r="W18" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.228</v>
+        <v>1.1897</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6567</v>
+        <v>-0.6609</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.5921</v>
+        <v>-0.95</v>
       </c>
       <c r="F19" t="n">
-        <v>4.9353</v>
+        <v>0.289</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3165</v>
+        <v>-0.2898</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3539</v>
+        <v>-0.1563</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6705</v>
+        <v>-0.1335</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1833</v>
+        <v>-1.004</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0205</v>
+        <v>-0.3364</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1628</v>
+        <v>-0.6676</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4998</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3335</v>
+        <v>0.1801</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8333</v>
+        <v>0.5341</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.579</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-4.8252</v>
-      </c>
       <c r="R19" t="n">
-        <v>3.8602</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8507</v>
+        <v>0.2079</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.236</v>
+        <v>-0.2089</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3853</v>
+        <v>0.4167</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4755</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="X19" t="n">
-        <v>1.1897</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.381</v>
+        <v>-1.6288</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4708</v>
+        <v>-2.3706</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0898</v>
+        <v>0.7418</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4379</v>
@@ -2014,13 +2014,13 @@
         <v>3.6672</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3774</v>
+        <v>0.1296</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.236</v>
+        <v>-1.1359</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6134</v>
+        <v>1.2654</v>
       </c>
       <c r="V20" t="n">
         <v>-2.8646</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2674</v>
+        <v>-3.3269</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4383</v>
+        <v>-1.7388</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.829</v>
+        <v>-1.5881</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0275</v>
@@ -2092,13 +2092,13 @@
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1976</v>
+        <v>-0.2571</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2247</v>
+        <v>-0.5251</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0271</v>
+        <v>0.268</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6562</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4311</v>
+        <v>-3.9401</v>
       </c>
       <c r="E22" t="n">
         <v>-5.564</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1329</v>
+        <v>1.6239</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0632</v>
@@ -2170,13 +2170,13 @@
         <v>1.7371</v>
       </c>
       <c r="S22" t="n">
-        <v>1.088</v>
+        <v>0.579</v>
       </c>
       <c r="T22" t="n">
         <v>-0.7601</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8481</v>
+        <v>1.3391</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2429</v>
+        <v>-5.2273</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0528</v>
+        <v>-3.6523</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.19</v>
+        <v>-1.575</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2269</v>
@@ -2248,13 +2248,13 @@
         <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2089</v>
+        <v>-0.1933</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0708</v>
+        <v>-0.6702</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1382</v>
+        <v>0.4769</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6455</v>
+        <v>-3.310300000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-23.5885</v>
+        <v>-23.5888</v>
       </c>
       <c r="F24" t="n">
-        <v>18.9431</v>
+        <v>20.2784</v>
       </c>
       <c r="G24" t="n">
         <v>-14.2153</v>
@@ -2326,13 +2326,13 @@
         <v>24.1262</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8572</v>
+        <v>-0.5221000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.7464</v>
+        <v>-7.7465</v>
       </c>
       <c r="U24" t="n">
-        <v>5.8891</v>
+        <v>7.2243</v>
       </c>
       <c r="V24" t="n">
         <v>2.7418</v>
